--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756466</v>
+        <v>121756483</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>56561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477264</v>
+        <v>477265</v>
       </c>
       <c r="R2" t="n">
-        <v>6593349</v>
+        <v>6593329</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +779,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756419</v>
+        <v>121756466</v>
       </c>
       <c r="B3" t="n">
         <v>90693</v>
@@ -824,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477262</v>
+        <v>477264</v>
       </c>
       <c r="R3" t="n">
-        <v>6593433</v>
+        <v>6593349</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756494</v>
+        <v>121756419</v>
       </c>
       <c r="B4" t="n">
         <v>90693</v>
@@ -930,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477195</v>
+        <v>477262</v>
       </c>
       <c r="R4" t="n">
-        <v>6593346</v>
+        <v>6593433</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756483</v>
+        <v>121756494</v>
       </c>
       <c r="B5" t="n">
-        <v>56561</v>
+        <v>90693</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,58 +1021,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477265</v>
+        <v>477195</v>
       </c>
       <c r="R5" t="n">
-        <v>6593329</v>
+        <v>6593346</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1097,6 +1096,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756483</v>
+        <v>121756494</v>
       </c>
       <c r="B2" t="n">
-        <v>56561</v>
+        <v>90693</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477265</v>
+        <v>477195</v>
       </c>
       <c r="R2" t="n">
-        <v>6593329</v>
+        <v>6593346</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756466</v>
+        <v>121756419</v>
       </c>
       <c r="B3" t="n">
         <v>90693</v>
@@ -840,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477264</v>
+        <v>477262</v>
       </c>
       <c r="R3" t="n">
-        <v>6593349</v>
+        <v>6593433</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756419</v>
+        <v>121756483</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>56561</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,41 +899,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477262</v>
+        <v>477265</v>
       </c>
       <c r="R4" t="n">
-        <v>6593433</v>
+        <v>6593329</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756494</v>
+        <v>121756466</v>
       </c>
       <c r="B5" t="n">
         <v>90693</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477195</v>
+        <v>477264</v>
       </c>
       <c r="R5" t="n">
-        <v>6593346</v>
+        <v>6593349</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756419</v>
+        <v>121756483</v>
       </c>
       <c r="B3" t="n">
-        <v>90693</v>
+        <v>56561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +793,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477262</v>
+        <v>477265</v>
       </c>
       <c r="R3" t="n">
-        <v>6593433</v>
+        <v>6593329</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756483</v>
+        <v>121756419</v>
       </c>
       <c r="B4" t="n">
-        <v>56561</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,58 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477265</v>
+        <v>477262</v>
       </c>
       <c r="R4" t="n">
-        <v>6593329</v>
+        <v>6593433</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756494</v>
+        <v>121756483</v>
       </c>
       <c r="B2" t="n">
-        <v>90693</v>
+        <v>56561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477195</v>
+        <v>477265</v>
       </c>
       <c r="R2" t="n">
-        <v>6593346</v>
+        <v>6593329</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +779,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756483</v>
+        <v>121756419</v>
       </c>
       <c r="B3" t="n">
-        <v>56561</v>
+        <v>90693</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,58 +809,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477265</v>
+        <v>477262</v>
       </c>
       <c r="R3" t="n">
-        <v>6593329</v>
+        <v>6593433</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756419</v>
+        <v>121756494</v>
       </c>
       <c r="B4" t="n">
         <v>90693</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477262</v>
+        <v>477195</v>
       </c>
       <c r="R4" t="n">
-        <v>6593433</v>
+        <v>6593346</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121756483</v>
       </c>
       <c r="B2" t="n">
-        <v>56561</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756419</v>
+        <v>121756494</v>
       </c>
       <c r="B3" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477262</v>
+        <v>477195</v>
       </c>
       <c r="R3" t="n">
-        <v>6593433</v>
+        <v>6593346</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756494</v>
+        <v>121756466</v>
       </c>
       <c r="B4" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477195</v>
+        <v>477264</v>
       </c>
       <c r="R4" t="n">
-        <v>6593346</v>
+        <v>6593349</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756466</v>
+        <v>121756419</v>
       </c>
       <c r="B5" t="n">
-        <v>90693</v>
+        <v>90707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477264</v>
+        <v>477262</v>
       </c>
       <c r="R5" t="n">
-        <v>6593349</v>
+        <v>6593433</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756483</v>
+        <v>121756494</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>90709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477265</v>
+        <v>477195</v>
       </c>
       <c r="R2" t="n">
-        <v>6593329</v>
+        <v>6593346</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756494</v>
+        <v>121756483</v>
       </c>
       <c r="B3" t="n">
-        <v>90707</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,41 +793,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477195</v>
+        <v>477265</v>
       </c>
       <c r="R3" t="n">
-        <v>6593346</v>
+        <v>6593329</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -906,7 +906,7 @@
         <v>121756466</v>
       </c>
       <c r="B4" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>121756419</v>
       </c>
       <c r="B5" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756494</v>
+        <v>121756419</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477195</v>
+        <v>477262</v>
       </c>
       <c r="R2" t="n">
-        <v>6593346</v>
+        <v>6593433</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756466</v>
+        <v>121756494</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477264</v>
+        <v>477195</v>
       </c>
       <c r="R4" t="n">
-        <v>6593349</v>
+        <v>6593346</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756419</v>
+        <v>121756466</v>
       </c>
       <c r="B5" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477262</v>
+        <v>477264</v>
       </c>
       <c r="R5" t="n">
-        <v>6593433</v>
+        <v>6593349</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756419</v>
+        <v>121756483</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>56573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477262</v>
+        <v>477265</v>
       </c>
       <c r="R2" t="n">
-        <v>6593433</v>
+        <v>6593329</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +779,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756483</v>
+        <v>121756494</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>90719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,58 +809,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477265</v>
+        <v>477195</v>
       </c>
       <c r="R3" t="n">
-        <v>6593329</v>
+        <v>6593346</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756494</v>
+        <v>121756419</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477195</v>
+        <v>477262</v>
       </c>
       <c r="R4" t="n">
-        <v>6593346</v>
+        <v>6593433</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1012,7 +1012,7 @@
         <v>121756466</v>
       </c>
       <c r="B5" t="n">
-        <v>90710</v>
+        <v>90719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756483</v>
+        <v>121756494</v>
       </c>
       <c r="B2" t="n">
-        <v>56573</v>
+        <v>90726</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,58 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477265</v>
+        <v>477195</v>
       </c>
       <c r="R2" t="n">
-        <v>6593329</v>
+        <v>6593346</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -779,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756494</v>
+        <v>121756419</v>
       </c>
       <c r="B3" t="n">
-        <v>90719</v>
+        <v>90726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -840,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477195</v>
+        <v>477262</v>
       </c>
       <c r="R3" t="n">
-        <v>6593346</v>
+        <v>6593433</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756419</v>
+        <v>121756483</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>56574</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,41 +899,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477262</v>
+        <v>477265</v>
       </c>
       <c r="R4" t="n">
-        <v>6593433</v>
+        <v>6593329</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>121756466</v>
       </c>
       <c r="B5" t="n">
-        <v>90719</v>
+        <v>90726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121756494</v>
+        <v>121756419</v>
       </c>
       <c r="B2" t="n">
-        <v>90726</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477195</v>
+        <v>477262</v>
       </c>
       <c r="R2" t="n">
-        <v>6593346</v>
+        <v>6593433</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121756419</v>
+        <v>121756483</v>
       </c>
       <c r="B3" t="n">
-        <v>90726</v>
+        <v>56576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,41 +793,58 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477262</v>
+        <v>477265</v>
       </c>
       <c r="R3" t="n">
-        <v>6593433</v>
+        <v>6593329</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -868,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121756483</v>
+        <v>121756466</v>
       </c>
       <c r="B4" t="n">
-        <v>56574</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,58 +915,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477265</v>
+        <v>477264</v>
       </c>
       <c r="R4" t="n">
-        <v>6593329</v>
+        <v>6593349</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121756466</v>
+        <v>121756494</v>
       </c>
       <c r="B5" t="n">
-        <v>90726</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477264</v>
+        <v>477195</v>
       </c>
       <c r="R5" t="n">
-        <v>6593349</v>
+        <v>6593346</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1113,6 +1113,541 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122777181</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78499</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477198</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6593541</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122776639</v>
+      </c>
+      <c r="B7" t="n">
+        <v>94748</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477243</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6593278</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122777199</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79351</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477193</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6593547</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122776681</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477192</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6593453</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122777162</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>477213</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6593502</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2291,6 +2291,219 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122853559</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90905</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477063</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6593395</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122853545</v>
+      </c>
+      <c r="B18" t="n">
+        <v>95884</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>54</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skogstrappmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anastrophyllum michauxii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(F.Weber.) H.Buch</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>477093</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6593408</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122776639</v>
+        <v>122777181</v>
       </c>
       <c r="B6" t="n">
-        <v>94748</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,31 +1127,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477243</v>
+        <v>477198</v>
       </c>
       <c r="R6" t="n">
-        <v>6593278</v>
+        <v>6593541</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122777199</v>
+        <v>122776681</v>
       </c>
       <c r="B7" t="n">
-        <v>79351</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,26 +1237,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477193</v>
+        <v>477192</v>
       </c>
       <c r="R7" t="n">
-        <v>6593547</v>
+        <v>6593453</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,7 +1313,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1328,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777162</v>
+        <v>122776639</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>94756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,30 +1343,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1371,13 +1375,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477213</v>
+        <v>477243</v>
       </c>
       <c r="R8" t="n">
-        <v>6593502</v>
+        <v>6593278</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776681</v>
+        <v>122777199</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>79355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,31 +1454,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477192</v>
+        <v>477193</v>
       </c>
       <c r="R9" t="n">
-        <v>6593453</v>
+        <v>6593547</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122777181</v>
+        <v>122777162</v>
       </c>
       <c r="B10" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477198</v>
+        <v>477213</v>
       </c>
       <c r="R10" t="n">
-        <v>6593541</v>
+        <v>6593502</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815670</v>
+        <v>122815664</v>
       </c>
       <c r="B12" t="n">
-        <v>95893</v>
+        <v>78502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,27 +1778,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477226</v>
+        <v>477123</v>
       </c>
       <c r="R12" t="n">
-        <v>6593513</v>
+        <v>6593435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815664</v>
+        <v>122815679</v>
       </c>
       <c r="B13" t="n">
-        <v>78498</v>
+        <v>78929</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,25 +1880,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1912,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477123</v>
+        <v>477182</v>
       </c>
       <c r="R13" t="n">
-        <v>6593435</v>
+        <v>6593531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1978,7 +1977,7 @@
         <v>122815677</v>
       </c>
       <c r="B14" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815679</v>
+        <v>122815665</v>
       </c>
       <c r="B15" t="n">
-        <v>78925</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2092,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477182</v>
+        <v>477230</v>
       </c>
       <c r="R15" t="n">
-        <v>6593531</v>
+        <v>6593499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815665</v>
+        <v>122815670</v>
       </c>
       <c r="B16" t="n">
-        <v>78498</v>
+        <v>95901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,26 +2202,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477230</v>
+        <v>477226</v>
       </c>
       <c r="R16" t="n">
-        <v>6593499</v>
+        <v>6593513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>122853559</v>
       </c>
       <c r="B17" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>122853545</v>
       </c>
       <c r="B18" t="n">
-        <v>95884</v>
+        <v>95892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2080,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815665</v>
+        <v>122815670</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>95901</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,26 +2096,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2123,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477230</v>
+        <v>477226</v>
       </c>
       <c r="R15" t="n">
-        <v>6593499</v>
+        <v>6593513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815670</v>
+        <v>122815665</v>
       </c>
       <c r="B16" t="n">
-        <v>95901</v>
+        <v>78502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,27 +2203,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477226</v>
+        <v>477230</v>
       </c>
       <c r="R16" t="n">
-        <v>6593513</v>
+        <v>6593499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777181</v>
+        <v>122776681</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,26 +1131,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477198</v>
+        <v>477192</v>
       </c>
       <c r="R6" t="n">
-        <v>6593541</v>
+        <v>6593453</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1207,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122776681</v>
+        <v>122777181</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>78503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,31 +1241,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,13 +1268,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477192</v>
+        <v>477198</v>
       </c>
       <c r="R7" t="n">
-        <v>6593453</v>
+        <v>6593541</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,6 +1312,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122776639</v>
+        <v>122777199</v>
       </c>
       <c r="B8" t="n">
-        <v>94756</v>
+        <v>79355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,31 +1343,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477243</v>
+        <v>477193</v>
       </c>
       <c r="R8" t="n">
-        <v>6593278</v>
+        <v>6593547</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122777199</v>
+        <v>122777162</v>
       </c>
       <c r="B9" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477193</v>
+        <v>477213</v>
       </c>
       <c r="R9" t="n">
-        <v>6593547</v>
+        <v>6593502</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122777162</v>
+        <v>122776639</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>94756</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,30 +1555,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477213</v>
+        <v>477243</v>
       </c>
       <c r="R10" t="n">
-        <v>6593502</v>
+        <v>6593278</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815664</v>
+        <v>122815665</v>
       </c>
       <c r="B12" t="n">
         <v>78502</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477123</v>
+        <v>477230</v>
       </c>
       <c r="R12" t="n">
-        <v>6593435</v>
+        <v>6593499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815679</v>
+        <v>122815670</v>
       </c>
       <c r="B13" t="n">
-        <v>78929</v>
+        <v>95901</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,30 +1880,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477182</v>
+        <v>477226</v>
       </c>
       <c r="R13" t="n">
-        <v>6593531</v>
+        <v>6593513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,7 +1975,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815677</v>
+        <v>122815664</v>
       </c>
       <c r="B14" t="n">
         <v>78502</v>
@@ -2017,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477217</v>
+        <v>477123</v>
       </c>
       <c r="R14" t="n">
-        <v>6593508</v>
+        <v>6593435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815670</v>
+        <v>122815677</v>
       </c>
       <c r="B15" t="n">
-        <v>95901</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,27 +2097,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477226</v>
+        <v>477217</v>
       </c>
       <c r="R15" t="n">
-        <v>6593513</v>
+        <v>6593508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815665</v>
+        <v>122815679</v>
       </c>
       <c r="B16" t="n">
-        <v>78502</v>
+        <v>78929</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,25 +2199,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477230</v>
+        <v>477182</v>
       </c>
       <c r="R16" t="n">
-        <v>6593499</v>
+        <v>6593531</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122853559</v>
+        <v>122853545</v>
       </c>
       <c r="B17" t="n">
-        <v>90909</v>
+        <v>95892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,30 +2305,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2336,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477063</v>
+        <v>477093</v>
       </c>
       <c r="R17" t="n">
-        <v>6593395</v>
+        <v>6593408</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122853545</v>
+        <v>122853559</v>
       </c>
       <c r="B18" t="n">
-        <v>95892</v>
+        <v>90909</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,31 +2412,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477093</v>
+        <v>477063</v>
       </c>
       <c r="R18" t="n">
-        <v>6593408</v>
+        <v>6593395</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122776681</v>
+        <v>122777162</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,31 +1131,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1163,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477192</v>
+        <v>477213</v>
       </c>
       <c r="R6" t="n">
-        <v>6593453</v>
+        <v>6593502</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,6 +1202,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1225,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122777181</v>
+        <v>122776639</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
+        <v>94758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,30 +1233,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1268,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477198</v>
+        <v>477243</v>
       </c>
       <c r="R7" t="n">
-        <v>6593541</v>
+        <v>6593278</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777199</v>
+        <v>122776681</v>
       </c>
       <c r="B8" t="n">
-        <v>79355</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,26 +1344,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1374,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477193</v>
+        <v>477192</v>
       </c>
       <c r="R8" t="n">
-        <v>6593547</v>
+        <v>6593453</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,7 +1420,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1437,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122777162</v>
+        <v>122777199</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,21 +1454,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477213</v>
+        <v>477193</v>
       </c>
       <c r="R9" t="n">
-        <v>6593502</v>
+        <v>6593547</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122776639</v>
+        <v>122777181</v>
       </c>
       <c r="B10" t="n">
-        <v>94756</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,31 +1556,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477243</v>
+        <v>477198</v>
       </c>
       <c r="R10" t="n">
-        <v>6593278</v>
+        <v>6593541</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815665</v>
+        <v>122815664</v>
       </c>
       <c r="B12" t="n">
         <v>78502</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477230</v>
+        <v>477123</v>
       </c>
       <c r="R12" t="n">
-        <v>6593499</v>
+        <v>6593435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815670</v>
+        <v>122815677</v>
       </c>
       <c r="B13" t="n">
-        <v>95901</v>
+        <v>78502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,27 +1884,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477226</v>
+        <v>477217</v>
       </c>
       <c r="R13" t="n">
-        <v>6593513</v>
+        <v>6593508</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,7 +1974,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815664</v>
+        <v>122815665</v>
       </c>
       <c r="B14" t="n">
         <v>78502</v>
@@ -2018,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477123</v>
+        <v>477230</v>
       </c>
       <c r="R14" t="n">
-        <v>6593435</v>
+        <v>6593499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2080,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815677</v>
+        <v>122815670</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>95903</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,26 +2096,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477217</v>
+        <v>477226</v>
       </c>
       <c r="R15" t="n">
-        <v>6593508</v>
+        <v>6593513</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122853545</v>
+        <v>122853559</v>
       </c>
       <c r="B17" t="n">
-        <v>95892</v>
+        <v>90909</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,31 +2305,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2337,10 +2336,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477093</v>
+        <v>477063</v>
       </c>
       <c r="R17" t="n">
-        <v>6593408</v>
+        <v>6593395</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2399,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122853559</v>
+        <v>122853545</v>
       </c>
       <c r="B18" t="n">
-        <v>90909</v>
+        <v>95894</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,30 +2411,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477063</v>
+        <v>477093</v>
       </c>
       <c r="R18" t="n">
-        <v>6593395</v>
+        <v>6593408</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1328,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122776681</v>
+        <v>122777199</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>79355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,31 +1344,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477192</v>
+        <v>477193</v>
       </c>
       <c r="R8" t="n">
-        <v>6593453</v>
+        <v>6593547</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,6 +1415,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1438,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122777199</v>
+        <v>122776681</v>
       </c>
       <c r="B9" t="n">
-        <v>79355</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,26 +1450,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477193</v>
+        <v>477192</v>
       </c>
       <c r="R9" t="n">
-        <v>6593547</v>
+        <v>6593453</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1525,7 +1526,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1328,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777199</v>
+        <v>122776681</v>
       </c>
       <c r="B8" t="n">
-        <v>79355</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,26 +1344,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1371,13 +1376,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477193</v>
+        <v>477192</v>
       </c>
       <c r="R8" t="n">
-        <v>6593547</v>
+        <v>6593453</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,7 +1420,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1434,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776681</v>
+        <v>122777199</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>79355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,31 +1454,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477192</v>
+        <v>477193</v>
       </c>
       <c r="R9" t="n">
-        <v>6593453</v>
+        <v>6593547</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777162</v>
+        <v>122777199</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>79355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477213</v>
+        <v>477193</v>
       </c>
       <c r="R6" t="n">
-        <v>6593502</v>
+        <v>6593547</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122776639</v>
+        <v>122777162</v>
       </c>
       <c r="B7" t="n">
-        <v>94758</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1233,31 +1233,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1265,13 +1264,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477243</v>
+        <v>477213</v>
       </c>
       <c r="R7" t="n">
-        <v>6593278</v>
+        <v>6593502</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777199</v>
+        <v>122777181</v>
       </c>
       <c r="B8" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1344,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477193</v>
+        <v>477198</v>
       </c>
       <c r="R8" t="n">
-        <v>6593547</v>
+        <v>6593541</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1434,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776681</v>
+        <v>122776639</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>94758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,35 +1445,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477192</v>
+        <v>477243</v>
       </c>
       <c r="R9" t="n">
-        <v>6593453</v>
+        <v>6593278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,6 +1521,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122777181</v>
+        <v>122776681</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,26 +1556,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477198</v>
+        <v>477192</v>
       </c>
       <c r="R10" t="n">
-        <v>6593541</v>
+        <v>6593453</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1632,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815664</v>
+        <v>122815670</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
+        <v>95903</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,26 +1778,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1805,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477123</v>
+        <v>477226</v>
       </c>
       <c r="R12" t="n">
-        <v>6593435</v>
+        <v>6593513</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1869,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815677</v>
+        <v>122815665</v>
       </c>
       <c r="B13" t="n">
         <v>78502</v>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477217</v>
+        <v>477230</v>
       </c>
       <c r="R13" t="n">
-        <v>6593508</v>
+        <v>6593499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815665</v>
+        <v>122815679</v>
       </c>
       <c r="B14" t="n">
-        <v>78502</v>
+        <v>78929</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1987,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477230</v>
+        <v>477182</v>
       </c>
       <c r="R14" t="n">
-        <v>6593499</v>
+        <v>6593531</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815670</v>
+        <v>122815664</v>
       </c>
       <c r="B15" t="n">
-        <v>95903</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,27 +2097,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477226</v>
+        <v>477123</v>
       </c>
       <c r="R15" t="n">
-        <v>6593513</v>
+        <v>6593435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815679</v>
+        <v>122815677</v>
       </c>
       <c r="B16" t="n">
-        <v>78929</v>
+        <v>78502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,25 +2199,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477182</v>
+        <v>477217</v>
       </c>
       <c r="R16" t="n">
-        <v>6593531</v>
+        <v>6593508</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777199</v>
+        <v>122777181</v>
       </c>
       <c r="B6" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477193</v>
+        <v>477198</v>
       </c>
       <c r="R6" t="n">
-        <v>6593547</v>
+        <v>6593541</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777181</v>
+        <v>122776639</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>94766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1339,30 +1339,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,13 +1371,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477198</v>
+        <v>477243</v>
       </c>
       <c r="R8" t="n">
-        <v>6593541</v>
+        <v>6593278</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1433,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776639</v>
+        <v>122776681</v>
       </c>
       <c r="B9" t="n">
-        <v>94758</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,31 +1446,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1477,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477243</v>
+        <v>477192</v>
       </c>
       <c r="R9" t="n">
-        <v>6593278</v>
+        <v>6593453</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1526,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122776681</v>
+        <v>122777199</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>79355</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,31 +1560,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477192</v>
+        <v>477193</v>
       </c>
       <c r="R10" t="n">
-        <v>6593453</v>
+        <v>6593547</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,6 +1631,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815670</v>
+        <v>122815665</v>
       </c>
       <c r="B12" t="n">
-        <v>95903</v>
+        <v>78502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,27 +1778,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477226</v>
+        <v>477230</v>
       </c>
       <c r="R12" t="n">
-        <v>6593513</v>
+        <v>6593499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,7 +1868,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815665</v>
+        <v>122815664</v>
       </c>
       <c r="B13" t="n">
         <v>78502</v>
@@ -1912,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477230</v>
+        <v>477123</v>
       </c>
       <c r="R13" t="n">
-        <v>6593499</v>
+        <v>6593435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815679</v>
+        <v>122815670</v>
       </c>
       <c r="B14" t="n">
-        <v>78929</v>
+        <v>95911</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1987,30 +1986,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1249</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477182</v>
+        <v>477226</v>
       </c>
       <c r="R14" t="n">
-        <v>6593531</v>
+        <v>6593513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815664</v>
+        <v>122815677</v>
       </c>
       <c r="B15" t="n">
         <v>78502</v>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477123</v>
+        <v>477217</v>
       </c>
       <c r="R15" t="n">
-        <v>6593435</v>
+        <v>6593508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815677</v>
+        <v>122815679</v>
       </c>
       <c r="B16" t="n">
-        <v>78502</v>
+        <v>78929</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,25 +2199,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477217</v>
+        <v>477182</v>
       </c>
       <c r="R16" t="n">
-        <v>6593508</v>
+        <v>6593531</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>122853559</v>
       </c>
       <c r="B17" t="n">
-        <v>90909</v>
+        <v>90917</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>122853545</v>
       </c>
       <c r="B18" t="n">
-        <v>95894</v>
+        <v>95902</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777181</v>
+        <v>122777199</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>79355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477198</v>
+        <v>477193</v>
       </c>
       <c r="R6" t="n">
-        <v>6593541</v>
+        <v>6593547</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122777162</v>
+        <v>122776681</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,26 +1237,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1264,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477213</v>
+        <v>477192</v>
       </c>
       <c r="R7" t="n">
-        <v>6593502</v>
+        <v>6593453</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,7 +1313,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1434,10 +1438,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776681</v>
+        <v>122777181</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,31 +1454,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477192</v>
+        <v>477198</v>
       </c>
       <c r="R9" t="n">
-        <v>6593453</v>
+        <v>6593541</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122777199</v>
+        <v>122777162</v>
       </c>
       <c r="B10" t="n">
-        <v>79355</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477193</v>
+        <v>477213</v>
       </c>
       <c r="R10" t="n">
-        <v>6593547</v>
+        <v>6593502</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815665</v>
+        <v>122815677</v>
       </c>
       <c r="B12" t="n">
         <v>78502</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477230</v>
+        <v>477217</v>
       </c>
       <c r="R12" t="n">
-        <v>6593499</v>
+        <v>6593508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815664</v>
+        <v>122815679</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
+        <v>78925</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,25 +1880,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477123</v>
+        <v>477182</v>
       </c>
       <c r="R13" t="n">
-        <v>6593435</v>
+        <v>6593531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815670</v>
+        <v>122815665</v>
       </c>
       <c r="B14" t="n">
-        <v>95911</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,27 +1990,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477226</v>
+        <v>477230</v>
       </c>
       <c r="R14" t="n">
-        <v>6593513</v>
+        <v>6593499</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,7 +2080,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815677</v>
+        <v>122815664</v>
       </c>
       <c r="B15" t="n">
         <v>78502</v>
@@ -2124,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477217</v>
+        <v>477123</v>
       </c>
       <c r="R15" t="n">
-        <v>6593508</v>
+        <v>6593435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815679</v>
+        <v>122815670</v>
       </c>
       <c r="B16" t="n">
-        <v>78929</v>
+        <v>95911</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,30 +2198,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1249</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477182</v>
+        <v>477226</v>
       </c>
       <c r="R16" t="n">
-        <v>6593531</v>
+        <v>6593513</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2293,10 +2293,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122853559</v>
+        <v>122853545</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>95902</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2305,30 +2305,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>54</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogstrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anastrophyllum michauxii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(F.Weber.) H.Buch</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2336,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477063</v>
+        <v>477093</v>
       </c>
       <c r="R17" t="n">
-        <v>6593395</v>
+        <v>6593408</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2399,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122853545</v>
+        <v>122853559</v>
       </c>
       <c r="B18" t="n">
-        <v>95902</v>
+        <v>90917</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2411,31 +2412,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogstrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anastrophyllum michauxii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(F.Weber.) H.Buch</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477093</v>
+        <v>477063</v>
       </c>
       <c r="R18" t="n">
-        <v>6593408</v>
+        <v>6593395</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777199</v>
+        <v>122777181</v>
       </c>
       <c r="B6" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477193</v>
+        <v>477198</v>
       </c>
       <c r="R6" t="n">
-        <v>6593547</v>
+        <v>6593541</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122776639</v>
+        <v>122777199</v>
       </c>
       <c r="B8" t="n">
-        <v>94766</v>
+        <v>79355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,31 +1343,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1375,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477243</v>
+        <v>477193</v>
       </c>
       <c r="R8" t="n">
-        <v>6593278</v>
+        <v>6593547</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122777181</v>
+        <v>122776639</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>94766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,30 +1449,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,13 +1481,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477198</v>
+        <v>477243</v>
       </c>
       <c r="R9" t="n">
-        <v>6593541</v>
+        <v>6593278</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815677</v>
+        <v>122815679</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
+        <v>78925</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,25 +1774,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477217</v>
+        <v>477182</v>
       </c>
       <c r="R12" t="n">
-        <v>6593508</v>
+        <v>6593531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815679</v>
+        <v>122815677</v>
       </c>
       <c r="B13" t="n">
-        <v>78925</v>
+        <v>78502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,25 +1880,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477182</v>
+        <v>477217</v>
       </c>
       <c r="R13" t="n">
-        <v>6593531</v>
+        <v>6593508</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815665</v>
+        <v>122815670</v>
       </c>
       <c r="B14" t="n">
-        <v>78502</v>
+        <v>95911</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,26 +1990,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2017,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477230</v>
+        <v>477226</v>
       </c>
       <c r="R14" t="n">
-        <v>6593499</v>
+        <v>6593513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2080,7 +2081,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815664</v>
+        <v>122815665</v>
       </c>
       <c r="B15" t="n">
         <v>78502</v>
@@ -2123,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477123</v>
+        <v>477230</v>
       </c>
       <c r="R15" t="n">
-        <v>6593435</v>
+        <v>6593499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2186,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815670</v>
+        <v>122815664</v>
       </c>
       <c r="B16" t="n">
-        <v>95911</v>
+        <v>78502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,27 +2203,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477226</v>
+        <v>477123</v>
       </c>
       <c r="R16" t="n">
-        <v>6593513</v>
+        <v>6593435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777181</v>
+        <v>122776639</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>94766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,30 +1127,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1158,13 +1159,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477198</v>
+        <v>477243</v>
       </c>
       <c r="R6" t="n">
-        <v>6593541</v>
+        <v>6593278</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122776681</v>
+        <v>122777199</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>79355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,31 +1238,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1269,13 +1265,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477192</v>
+        <v>477193</v>
       </c>
       <c r="R7" t="n">
-        <v>6593453</v>
+        <v>6593547</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,6 +1309,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1331,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777199</v>
+        <v>122777181</v>
       </c>
       <c r="B8" t="n">
-        <v>79355</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477193</v>
+        <v>477198</v>
       </c>
       <c r="R8" t="n">
-        <v>6593547</v>
+        <v>6593541</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776639</v>
+        <v>122776681</v>
       </c>
       <c r="B9" t="n">
-        <v>94766</v>
+        <v>57631</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,31 +1446,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477243</v>
+        <v>477192</v>
       </c>
       <c r="R9" t="n">
-        <v>6593278</v>
+        <v>6593453</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,7 +1526,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815679</v>
+        <v>122815677</v>
       </c>
       <c r="B12" t="n">
-        <v>78925</v>
+        <v>78502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,25 +1774,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477182</v>
+        <v>477217</v>
       </c>
       <c r="R12" t="n">
-        <v>6593531</v>
+        <v>6593508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815677</v>
+        <v>122815670</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
+        <v>95911</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,26 +1884,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477217</v>
+        <v>477226</v>
       </c>
       <c r="R13" t="n">
-        <v>6593508</v>
+        <v>6593513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815670</v>
+        <v>122815664</v>
       </c>
       <c r="B14" t="n">
-        <v>95911</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,27 +1991,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477226</v>
+        <v>477123</v>
       </c>
       <c r="R14" t="n">
-        <v>6593513</v>
+        <v>6593435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815665</v>
+        <v>122815679</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>78925</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2093,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477230</v>
+        <v>477182</v>
       </c>
       <c r="R15" t="n">
-        <v>6593499</v>
+        <v>6593531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,7 +2187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815664</v>
+        <v>122815665</v>
       </c>
       <c r="B16" t="n">
         <v>78502</v>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477123</v>
+        <v>477230</v>
       </c>
       <c r="R16" t="n">
-        <v>6593435</v>
+        <v>6593499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122776639</v>
+        <v>122777199</v>
       </c>
       <c r="B6" t="n">
-        <v>94766</v>
+        <v>79358</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,31 +1127,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,13 +1158,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477243</v>
+        <v>477193</v>
       </c>
       <c r="R6" t="n">
-        <v>6593278</v>
+        <v>6593547</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122777199</v>
+        <v>122777162</v>
       </c>
       <c r="B7" t="n">
-        <v>79355</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477193</v>
+        <v>477213</v>
       </c>
       <c r="R7" t="n">
-        <v>6593547</v>
+        <v>6593502</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1331,7 +1330,7 @@
         <v>122777181</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122776681</v>
+        <v>122776639</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>94769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,35 +1445,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477192</v>
+        <v>477243</v>
       </c>
       <c r="R9" t="n">
-        <v>6593453</v>
+        <v>6593278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1526,6 +1521,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122777162</v>
+        <v>122776681</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57634</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,26 +1556,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1587,13 +1588,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477213</v>
+        <v>477192</v>
       </c>
       <c r="R10" t="n">
-        <v>6593502</v>
+        <v>6593453</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,7 +1632,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>122799707</v>
       </c>
       <c r="B11" t="n">
-        <v>74855</v>
+        <v>74858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>122815677</v>
       </c>
       <c r="B12" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815670</v>
+        <v>122815679</v>
       </c>
       <c r="B13" t="n">
-        <v>95911</v>
+        <v>78928</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,31 +1880,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>1249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477226</v>
+        <v>477182</v>
       </c>
       <c r="R13" t="n">
-        <v>6593513</v>
+        <v>6593531</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815664</v>
+        <v>122815670</v>
       </c>
       <c r="B14" t="n">
-        <v>78502</v>
+        <v>95914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,26 +1990,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477123</v>
+        <v>477226</v>
       </c>
       <c r="R14" t="n">
-        <v>6593435</v>
+        <v>6593513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815679</v>
+        <v>122815665</v>
       </c>
       <c r="B15" t="n">
-        <v>78925</v>
+        <v>78505</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2093,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477182</v>
+        <v>477230</v>
       </c>
       <c r="R15" t="n">
-        <v>6593531</v>
+        <v>6593499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815665</v>
+        <v>122815664</v>
       </c>
       <c r="B16" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477230</v>
+        <v>477123</v>
       </c>
       <c r="R16" t="n">
-        <v>6593499</v>
+        <v>6593435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>122853545</v>
       </c>
       <c r="B17" t="n">
-        <v>95902</v>
+        <v>95905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>122853559</v>
       </c>
       <c r="B18" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1115,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122777199</v>
+        <v>122777162</v>
       </c>
       <c r="B6" t="n">
-        <v>79358</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477193</v>
+        <v>477213</v>
       </c>
       <c r="R6" t="n">
-        <v>6593547</v>
+        <v>6593502</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122777162</v>
+        <v>122777181</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477213</v>
+        <v>477198</v>
       </c>
       <c r="R7" t="n">
-        <v>6593502</v>
+        <v>6593541</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777181</v>
+        <v>122777199</v>
       </c>
       <c r="B8" t="n">
-        <v>78506</v>
+        <v>79360</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,21 +1343,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477198</v>
+        <v>477193</v>
       </c>
       <c r="R8" t="n">
-        <v>6593541</v>
+        <v>6593547</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1436,7 @@
         <v>122776639</v>
       </c>
       <c r="B9" t="n">
-        <v>94769</v>
+        <v>94771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815677</v>
+        <v>122815679</v>
       </c>
       <c r="B12" t="n">
-        <v>78505</v>
+        <v>78930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,25 +1774,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477217</v>
+        <v>477182</v>
       </c>
       <c r="R12" t="n">
-        <v>6593508</v>
+        <v>6593531</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815679</v>
+        <v>122815670</v>
       </c>
       <c r="B13" t="n">
-        <v>78928</v>
+        <v>95916</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1880,30 +1880,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1911,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477182</v>
+        <v>477226</v>
       </c>
       <c r="R13" t="n">
-        <v>6593531</v>
+        <v>6593513</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,10 +1975,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815670</v>
+        <v>122815664</v>
       </c>
       <c r="B14" t="n">
-        <v>95914</v>
+        <v>78507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,27 +1991,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477226</v>
+        <v>477123</v>
       </c>
       <c r="R14" t="n">
-        <v>6593513</v>
+        <v>6593435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815665</v>
+        <v>122815677</v>
       </c>
       <c r="B15" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477230</v>
+        <v>477217</v>
       </c>
       <c r="R15" t="n">
-        <v>6593499</v>
+        <v>6593508</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815664</v>
+        <v>122815665</v>
       </c>
       <c r="B16" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477123</v>
+        <v>477230</v>
       </c>
       <c r="R16" t="n">
-        <v>6593435</v>
+        <v>6593499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>122853545</v>
       </c>
       <c r="B17" t="n">
-        <v>95905</v>
+        <v>95907</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>122853559</v>
       </c>
       <c r="B18" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -1118,7 +1118,7 @@
         <v>122777162</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>122777181</v>
       </c>
       <c r="B7" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122777199</v>
+        <v>122776681</v>
       </c>
       <c r="B8" t="n">
-        <v>79360</v>
+        <v>57634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,26 +1343,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1370,13 +1375,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477193</v>
+        <v>477192</v>
       </c>
       <c r="R8" t="n">
-        <v>6593547</v>
+        <v>6593453</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,7 +1419,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1436,7 +1440,7 @@
         <v>122776639</v>
       </c>
       <c r="B9" t="n">
-        <v>94771</v>
+        <v>94777</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1540,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122776681</v>
+        <v>122777199</v>
       </c>
       <c r="B10" t="n">
-        <v>57634</v>
+        <v>79361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,31 +1560,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1588,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477192</v>
+        <v>477193</v>
       </c>
       <c r="R10" t="n">
-        <v>6593453</v>
+        <v>6593547</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1632,6 +1631,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122815679</v>
+        <v>122815677</v>
       </c>
       <c r="B12" t="n">
-        <v>78930</v>
+        <v>78508</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,25 +1774,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1249</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477182</v>
+        <v>477217</v>
       </c>
       <c r="R12" t="n">
-        <v>6593531</v>
+        <v>6593508</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122815670</v>
+        <v>122815665</v>
       </c>
       <c r="B13" t="n">
-        <v>95916</v>
+        <v>78508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,27 +1884,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1912,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477226</v>
+        <v>477230</v>
       </c>
       <c r="R13" t="n">
-        <v>6593513</v>
+        <v>6593499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122815664</v>
+        <v>122815670</v>
       </c>
       <c r="B14" t="n">
-        <v>78507</v>
+        <v>95922</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,26 +1990,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477123</v>
+        <v>477226</v>
       </c>
       <c r="R14" t="n">
-        <v>6593435</v>
+        <v>6593513</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122815677</v>
+        <v>122815679</v>
       </c>
       <c r="B15" t="n">
-        <v>78507</v>
+        <v>78931</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2093,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1249</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477217</v>
+        <v>477182</v>
       </c>
       <c r="R15" t="n">
-        <v>6593508</v>
+        <v>6593531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2187,10 +2187,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122815665</v>
+        <v>122815664</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
+        <v>78508</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477230</v>
+        <v>477123</v>
       </c>
       <c r="R16" t="n">
-        <v>6593499</v>
+        <v>6593435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2296,7 +2296,7 @@
         <v>122853545</v>
       </c>
       <c r="B17" t="n">
-        <v>95907</v>
+        <v>95913</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>122853559</v>
       </c>
       <c r="B18" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2504,6 +2504,555 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128372091</v>
+      </c>
+      <c r="B19" t="n">
+        <v>95715</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>477193</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6593370</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128375194</v>
+      </c>
+      <c r="B20" t="n">
+        <v>95705</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>477231</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6593281</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128375257</v>
+      </c>
+      <c r="B21" t="n">
+        <v>95705</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>477222</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6593223</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128371900</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4363</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Zontaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum concrescens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pers.) Banker</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>477195</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6593378</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128371708</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>477211</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6593371</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95715</v>
+        <v>95720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95705</v>
+        <v>95710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95705</v>
+        <v>95710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92641</v>
+        <v>92646</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3053,6 +3053,434 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128480483</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95710</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>477213</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6593215</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128480621</v>
+      </c>
+      <c r="B25" t="n">
+        <v>95710</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>477221</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6593261</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128483011</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91325</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>477327</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6593493</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128480612</v>
+      </c>
+      <c r="B27" t="n">
+        <v>95710</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477222</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6593263</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95720</v>
+        <v>95813</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92646</v>
+        <v>92738</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>128371708</v>
       </c>
       <c r="B23" t="n">
-        <v>56855</v>
+        <v>56867</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95710</v>
+        <v>95803</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91417</v>
+        <v>91423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95803</v>
+        <v>95809</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95813</v>
+        <v>95825</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95803</v>
+        <v>95815</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95803</v>
+        <v>95815</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92738</v>
+        <v>92750</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>128371708</v>
       </c>
       <c r="B23" t="n">
-        <v>56867</v>
+        <v>56871</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95809</v>
+        <v>95815</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95825</v>
+        <v>95827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92750</v>
+        <v>92752</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95815</v>
+        <v>95817</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95827</v>
+        <v>95828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92752</v>
+        <v>92753</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95817</v>
+        <v>95818</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3480,6 +3480,113 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128823323</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78873</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Båshöjden, Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>477211</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6593507</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95828</v>
+        <v>95855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95818</v>
+        <v>95845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92753</v>
+        <v>92780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>128371708</v>
       </c>
       <c r="B23" t="n">
-        <v>56871</v>
+        <v>56898</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95845</v>
+        <v>95851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>128823323</v>
       </c>
       <c r="B28" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95855</v>
+        <v>95868</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95845</v>
+        <v>95858</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95845</v>
+        <v>95858</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92780</v>
+        <v>92790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95851</v>
+        <v>95858</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>128823323</v>
       </c>
       <c r="B28" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95868</v>
+        <v>95872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95858</v>
+        <v>95862</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92790</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>128371708</v>
       </c>
       <c r="B23" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -2509,7 +2509,7 @@
         <v>128372091</v>
       </c>
       <c r="B19" t="n">
-        <v>95872</v>
+        <v>95879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>128375194</v>
       </c>
       <c r="B20" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>128375257</v>
       </c>
       <c r="B21" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>128371900</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>92799</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>128371708</v>
       </c>
       <c r="B23" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>128480483</v>
       </c>
       <c r="B24" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>128480621</v>
       </c>
       <c r="B25" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>128483011</v>
       </c>
       <c r="B26" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>128480612</v>
       </c>
       <c r="B27" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>128823323</v>
       </c>
       <c r="B28" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -3486,7 +3486,7 @@
         <v>128823323</v>
       </c>
       <c r="B28" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -3486,7 +3486,7 @@
         <v>128823323</v>
       </c>
       <c r="B28" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -3486,7 +3486,7 @@
         <v>128823323</v>
       </c>
       <c r="B28" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58020-2020 artfynd.xlsx
+++ b/artfynd/A 58020-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3588,6 +3588,127 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129529864</v>
+      </c>
+      <c r="B29" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Båshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>477238</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6593413</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Nils Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
